--- a/backend/docs/현행_DB_명세서.xlsx
+++ b/backend/docs/현행_DB_명세서.xlsx
@@ -22,7 +22,6 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="requirement_item(요구사항항목)" sheetId="13" state="visible" r:id="rId13"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="task_assignment(배정업무)" sheetId="14" state="visible" r:id="rId14"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="notification(알림)" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="재설계 검토 포인트" sheetId="16" state="visible" r:id="rId16"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -32,7 +31,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -68,11 +67,6 @@
     </font>
     <font>
       <name val="Consolas"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <i val="1"/>
-      <color rgb="009A6410"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -120,7 +114,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -133,9 +127,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -147,12 +139,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -519,17 +505,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="96" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="100" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>현행 DB 명세서</t>
+          <t>현행 DB 명세서 (DB 기준)</t>
         </is>
       </c>
       <c r="B1" s="2" t="inlineStr"/>
@@ -546,14 +532,14 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>MySQL 8 (utf8mb4) / AWS RDS</t>
+          <t>mysql / (8, 4, 9)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>스키마</t>
+          <t>스키마(NAME)</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -577,52 +563,52 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>앱</t>
+          <t>테이블 수</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>common · users · projects · meetings · requirements · tasks · notifications</t>
+          <t>13</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>테이블 수</t>
+          <t>기준</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>13 (Django 자동 생성 auth_* / django_* / M2M 조인 테이블 제외)</t>
+          <t>backend 모델 = DB (모든 마이그레이션 적용 완료 상태)</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>기준</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>backend/*/models.py + migrations (2026-09-07)</t>
-        </is>
-      </c>
+      <c r="A8" s="3" t="inlineStr"/>
+      <c r="B8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr"/>
-      <c r="B9" s="2" t="inlineStr"/>
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>표기</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>PK / FK(대상 table.col) / on_delete / NULL / UNIQUE / 기본값(now()=auto_now_add)</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>표기</t>
+          <t>최근 변경</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>bigint AI = BigAutoField(암시적 id) · int AI = AutoField(명시적 PK)</t>
+          <t>requirement_definition.project_id, requirement_item.category_2,</t>
         </is>
       </c>
     </row>
@@ -630,15 +616,7 @@
       <c r="A11" s="3" t="inlineStr"/>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>now() = auto_now_add · touch = auto_now</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr"/>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>PK / FK→대상 / on_delete(CASCADE·SET NULL) / NULL / UNIQUE</t>
+          <t>task_assignment 컬럼 전면 재설계, spec_document.evidence_data 추가</t>
         </is>
       </c>
     </row>
@@ -653,20 +631,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
     <col width="5" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="6" customWidth="1" min="7" max="7"/>
     <col width="8" customWidth="1" min="8" max="8"/>
     <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="60" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="46" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -676,10 +653,10 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="30" customHeight="1">
+    <row r="2" ht="26" customHeight="1">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>회의록 원문. AI 노드 1·2의 입력이자 상태(status) 관리 대상. 정렬: -created_at.</t>
+          <t>회의록 원문. AI 노드 1·2의 입력이자 상태 관리 대상.</t>
         </is>
       </c>
     </row>
@@ -732,11 +709,6 @@
       <c r="J3" s="4" t="inlineStr">
         <is>
           <t>설명</t>
-        </is>
-      </c>
-      <c r="K3" s="4" t="inlineStr">
-        <is>
-          <t>비고</t>
         </is>
       </c>
     </row>
@@ -751,7 +723,7 @@
       </c>
       <c r="C4" s="9" t="inlineStr">
         <is>
-          <t>int AI</t>
+          <t>integer AUTO_INCREMENT</t>
         </is>
       </c>
       <c r="D4" s="10" t="inlineStr">
@@ -769,7 +741,6 @@
           <t>회의록 ID</t>
         </is>
       </c>
-      <c r="K4" s="5" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="8" t="n">
@@ -788,7 +759,7 @@
       <c r="D5" s="8" t="inlineStr"/>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>project</t>
+          <t>project.id</t>
         </is>
       </c>
       <c r="F5" s="8" t="inlineStr">
@@ -802,13 +773,16 @@
         </is>
       </c>
       <c r="H5" s="8" t="inlineStr"/>
-      <c r="I5" s="9" t="inlineStr"/>
+      <c r="I5" s="9" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J5" s="5" t="inlineStr">
         <is>
           <t>소속 프로젝트</t>
         </is>
       </c>
-      <c r="K5" s="5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="8" t="n">
@@ -835,7 +809,6 @@
           <t>회의 제목</t>
         </is>
       </c>
-      <c r="K6" s="5" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="8" t="n">
@@ -859,10 +832,9 @@
       <c r="I7" s="9" t="inlineStr"/>
       <c r="J7" s="5" t="inlineStr">
         <is>
-          <t>회의록 원문 / 내용 (노드 1 입력)</t>
-        </is>
-      </c>
-      <c r="K7" s="5" t="inlineStr"/>
+          <t>회의록 원문/내용</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="8" t="n">
@@ -893,7 +865,6 @@
           <t>AI 핵심 요약</t>
         </is>
       </c>
-      <c r="K8" s="5" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="8" t="n">
@@ -924,7 +895,6 @@
           <t>회의 일시</t>
         </is>
       </c>
-      <c r="K9" s="5" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="8" t="n">
@@ -952,10 +922,9 @@
       <c r="I10" s="9" t="inlineStr"/>
       <c r="J10" s="5" t="inlineStr">
         <is>
-          <t>참석자 목록 (자유 텍스트)</t>
-        </is>
-      </c>
-      <c r="K10" s="5" t="inlineStr"/>
+          <t>참석자 목록</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="n">
@@ -978,15 +947,14 @@
       <c r="H11" s="8" t="inlineStr"/>
       <c r="I11" s="9" t="inlineStr">
         <is>
-          <t>DRAFT</t>
+          <t>MeetingNote.Status.DRAFT</t>
         </is>
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
-          <t>상태: DRAFT 작성 중 / PROCESSING AI 분석 중 / REVIEWED 검토 완료</t>
-        </is>
-      </c>
-      <c r="K11" s="5" t="inlineStr"/>
+          <t>상태  [DRAFT / PROCESSING / REVIEWED]</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="8" t="n">
@@ -1005,7 +973,7 @@
       <c r="D12" s="8" t="inlineStr"/>
       <c r="E12" s="8" t="inlineStr">
         <is>
-          <t>user</t>
+          <t>user.id</t>
         </is>
       </c>
       <c r="F12" s="8" t="inlineStr">
@@ -1021,7 +989,6 @@
           <t>작성자</t>
         </is>
       </c>
-      <c r="K12" s="5" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="8" t="n">
@@ -1052,7 +1019,6 @@
           <t>생성 일시</t>
         </is>
       </c>
-      <c r="K13" s="5" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="8" t="n">
@@ -1075,20 +1041,19 @@
       <c r="H14" s="8" t="inlineStr"/>
       <c r="I14" s="9" t="inlineStr">
         <is>
-          <t>touch</t>
+          <t>auto_now</t>
         </is>
       </c>
       <c r="J14" s="5" t="inlineStr">
         <is>
-          <t>수정 일시 (auto_now)</t>
-        </is>
-      </c>
-      <c r="K14" s="5" t="inlineStr"/>
+          <t>수정 일시</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:J2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1100,20 +1065,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K22"/>
+  <dimension ref="A1:J23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
     <col width="5" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="6" customWidth="1" min="7" max="7"/>
     <col width="8" customWidth="1" min="8" max="8"/>
     <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="60" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="46" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1123,10 +1087,10 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="30" customHeight="1">
+    <row r="2" ht="26" customHeight="1">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>회의록당 생성되는 기획서 초안. 7개 섹션을 각각 한 덩어리 텍스트로 저장(행 단위 저장 안 함). 정렬: -created_at.</t>
+          <t>회의록당 생성되는 기획서 초안(7섹션 텍스트 + 섹션별 근거 evidence_data).</t>
         </is>
       </c>
     </row>
@@ -1179,11 +1143,6 @@
       <c r="J3" s="4" t="inlineStr">
         <is>
           <t>설명</t>
-        </is>
-      </c>
-      <c r="K3" s="4" t="inlineStr">
-        <is>
-          <t>비고</t>
         </is>
       </c>
     </row>
@@ -1198,7 +1157,7 @@
       </c>
       <c r="C4" s="9" t="inlineStr">
         <is>
-          <t>int AI</t>
+          <t>integer AUTO_INCREMENT</t>
         </is>
       </c>
       <c r="D4" s="10" t="inlineStr">
@@ -1216,7 +1175,6 @@
           <t>기획서 ID</t>
         </is>
       </c>
-      <c r="K4" s="5" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="8" t="n">
@@ -1229,13 +1187,13 @@
       </c>
       <c r="C5" s="9" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr"/>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>meeting_note</t>
+          <t>meeting_note.meeting_id</t>
         </is>
       </c>
       <c r="F5" s="8" t="inlineStr">
@@ -1251,7 +1209,6 @@
           <t>관련 회의록</t>
         </is>
       </c>
-      <c r="K5" s="5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="8" t="n">
@@ -1278,7 +1235,6 @@
           <t>기획서 제목</t>
         </is>
       </c>
-      <c r="K6" s="5" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="8" t="n">
@@ -1309,7 +1265,6 @@
           <t>1. 프로젝트 개요</t>
         </is>
       </c>
-      <c r="K7" s="5" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="8" t="n">
@@ -1340,7 +1295,6 @@
           <t>2. 문제 정의</t>
         </is>
       </c>
-      <c r="K8" s="5" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="8" t="n">
@@ -1371,7 +1325,6 @@
           <t>3. 대상 사용자</t>
         </is>
       </c>
-      <c r="K9" s="5" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="8" t="n">
@@ -1402,7 +1355,6 @@
           <t>4. 주요 기능</t>
         </is>
       </c>
-      <c r="K10" s="5" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="8" t="n">
@@ -1433,7 +1385,6 @@
           <t>5. 사용자 시나리오</t>
         </is>
       </c>
-      <c r="K11" s="5" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="8" t="n">
@@ -1464,7 +1415,6 @@
           <t>6. 기술 스택 및 제약사항</t>
         </is>
       </c>
-      <c r="K12" s="5" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="8" t="n">
@@ -1495,7 +1445,6 @@
           <t>7. 최종 결정사항</t>
         </is>
       </c>
-      <c r="K13" s="5" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="8" t="n">
@@ -1503,12 +1452,12 @@
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>period_start</t>
+          <t>evidence_data</t>
         </is>
       </c>
       <c r="C14" s="9" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>longtext</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr"/>
@@ -1523,10 +1472,9 @@
       <c r="I14" s="9" t="inlineStr"/>
       <c r="J14" s="5" t="inlineStr">
         <is>
-          <t>프로젝트 시작일 (원문에서 정규식 추출)</t>
-        </is>
-      </c>
-      <c r="K14" s="5" t="inlineStr"/>
+          <t>섹션별 근거 데이터</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="n">
@@ -1534,7 +1482,7 @@
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>period_end</t>
+          <t>period_start</t>
         </is>
       </c>
       <c r="C15" s="9" t="inlineStr">
@@ -1554,78 +1502,67 @@
       <c r="I15" s="9" t="inlineStr"/>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t>프로젝트 종료일 (원문에서 정규식 추출)</t>
-        </is>
-      </c>
-      <c r="K15" s="5" t="inlineStr"/>
+          <t>프로젝트 시작일</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="11" t="n">
+      <c r="A16" s="8" t="n">
         <v>13</v>
       </c>
-      <c r="B16" s="11" t="inlineStr">
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>period_end</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr"/>
+      <c r="E16" s="8" t="inlineStr"/>
+      <c r="F16" s="8" t="inlineStr"/>
+      <c r="G16" s="8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H16" s="8" t="inlineStr"/>
+      <c r="I16" s="9" t="inlineStr"/>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>프로젝트 종료일</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" s="9" t="inlineStr">
         <is>
           <t>background</t>
         </is>
       </c>
-      <c r="C16" s="11" t="inlineStr">
+      <c r="C17" s="9" t="inlineStr">
         <is>
           <t>longtext</t>
         </is>
       </c>
-      <c r="D16" s="11" t="inlineStr"/>
-      <c r="E16" s="11" t="inlineStr"/>
-      <c r="F16" s="11" t="inlineStr"/>
-      <c r="G16" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H16" s="11" t="inlineStr"/>
-      <c r="I16" s="11" t="inlineStr"/>
-      <c r="J16" s="12" t="inlineStr">
-        <is>
-          <t>추진 배경</t>
-        </is>
-      </c>
-      <c r="K16" s="12" t="inlineStr">
-        <is>
-          <t>구 필드, 미사용</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="11" t="n">
-        <v>14</v>
-      </c>
-      <c r="B17" s="11" t="inlineStr">
-        <is>
-          <t>target_scope</t>
-        </is>
-      </c>
-      <c r="C17" s="11" t="inlineStr">
-        <is>
-          <t>longtext</t>
-        </is>
-      </c>
-      <c r="D17" s="11" t="inlineStr"/>
-      <c r="E17" s="11" t="inlineStr"/>
-      <c r="F17" s="11" t="inlineStr"/>
-      <c r="G17" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H17" s="11" t="inlineStr"/>
-      <c r="I17" s="11" t="inlineStr"/>
-      <c r="J17" s="12" t="inlineStr">
-        <is>
-          <t>개발 및 추진 범위</t>
-        </is>
-      </c>
-      <c r="K17" s="12" t="inlineStr">
-        <is>
-          <t>구 필드, 미사용</t>
+      <c r="D17" s="8" t="inlineStr"/>
+      <c r="E17" s="8" t="inlineStr"/>
+      <c r="F17" s="8" t="inlineStr"/>
+      <c r="G17" s="8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H17" s="8" t="inlineStr"/>
+      <c r="I17" s="9" t="inlineStr"/>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>추진 배경 (구 필드, 미사용)</t>
         </is>
       </c>
     </row>
@@ -1635,25 +1572,17 @@
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>status_code</t>
+          <t>target_scope</t>
         </is>
       </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
-          <t>varchar(50)</t>
+          <t>longtext</t>
         </is>
       </c>
       <c r="D18" s="8" t="inlineStr"/>
-      <c r="E18" s="8" t="inlineStr">
-        <is>
-          <t>common_code</t>
-        </is>
-      </c>
-      <c r="F18" s="8" t="inlineStr">
-        <is>
-          <t>SET NULL</t>
-        </is>
-      </c>
+      <c r="E18" s="8" t="inlineStr"/>
+      <c r="F18" s="8" t="inlineStr"/>
       <c r="G18" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -1663,10 +1592,9 @@
       <c r="I18" s="9" t="inlineStr"/>
       <c r="J18" s="5" t="inlineStr">
         <is>
-          <t>검토 상태 (draft / in_review / approved / rejected)</t>
-        </is>
-      </c>
-      <c r="K18" s="5" t="inlineStr"/>
+          <t>개발 및 추진 범위 (구 필드, 미사용)</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="8" t="n">
@@ -1674,18 +1602,18 @@
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>reviewer_id</t>
+          <t>status_code</t>
         </is>
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
-          <t>bigint</t>
+          <t>varchar(50)</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr"/>
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t>user</t>
+          <t>common_code.code_id</t>
         </is>
       </c>
       <c r="F19" s="8" t="inlineStr">
@@ -1699,13 +1627,16 @@
         </is>
       </c>
       <c r="H19" s="8" t="inlineStr"/>
-      <c r="I19" s="9" t="inlineStr"/>
+      <c r="I19" s="9" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J19" s="5" t="inlineStr">
         <is>
-          <t>검토자</t>
-        </is>
-      </c>
-      <c r="K19" s="5" t="inlineStr"/>
+          <t>검토 상태</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="8" t="n">
@@ -1713,30 +1644,41 @@
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>review_comment</t>
+          <t>reviewer_id</t>
         </is>
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
-          <t>longtext</t>
+          <t>bigint</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr"/>
-      <c r="E20" s="8" t="inlineStr"/>
-      <c r="F20" s="8" t="inlineStr"/>
+      <c r="E20" s="8" t="inlineStr">
+        <is>
+          <t>user.id</t>
+        </is>
+      </c>
+      <c r="F20" s="8" t="inlineStr">
+        <is>
+          <t>SET NULL</t>
+        </is>
+      </c>
       <c r="G20" s="8" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
       <c r="H20" s="8" t="inlineStr"/>
-      <c r="I20" s="9" t="inlineStr"/>
+      <c r="I20" s="9" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J20" s="5" t="inlineStr">
         <is>
-          <t>검토 의견 (반려 사유 등)</t>
-        </is>
-      </c>
-      <c r="K20" s="5" t="inlineStr"/>
+          <t>검토자</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="8" t="n">
@@ -1744,30 +1686,29 @@
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>review_comment</t>
         </is>
       </c>
       <c r="C21" s="9" t="inlineStr">
         <is>
-          <t>datetime(6)</t>
+          <t>longtext</t>
         </is>
       </c>
       <c r="D21" s="8" t="inlineStr"/>
       <c r="E21" s="8" t="inlineStr"/>
       <c r="F21" s="8" t="inlineStr"/>
-      <c r="G21" s="8" t="inlineStr"/>
+      <c r="G21" s="8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="H21" s="8" t="inlineStr"/>
-      <c r="I21" s="9" t="inlineStr">
-        <is>
-          <t>now()</t>
-        </is>
-      </c>
+      <c r="I21" s="9" t="inlineStr"/>
       <c r="J21" s="5" t="inlineStr">
         <is>
-          <t>생성 일시</t>
-        </is>
-      </c>
-      <c r="K21" s="5" t="inlineStr"/>
+          <t>검토 의견</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="8" t="n">
@@ -1775,7 +1716,7 @@
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>updated_at</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="C22" s="9" t="inlineStr">
@@ -1790,20 +1731,49 @@
       <c r="H22" s="8" t="inlineStr"/>
       <c r="I22" s="9" t="inlineStr">
         <is>
-          <t>touch</t>
+          <t>now()</t>
         </is>
       </c>
       <c r="J22" s="5" t="inlineStr">
         <is>
-          <t>수정 일시 (auto_now)</t>
-        </is>
-      </c>
-      <c r="K22" s="5" t="inlineStr"/>
+          <t>생성 일시</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>updated_at</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>datetime(6)</t>
+        </is>
+      </c>
+      <c r="D23" s="8" t="inlineStr"/>
+      <c r="E23" s="8" t="inlineStr"/>
+      <c r="F23" s="8" t="inlineStr"/>
+      <c r="G23" s="8" t="inlineStr"/>
+      <c r="H23" s="8" t="inlineStr"/>
+      <c r="I23" s="9" t="inlineStr">
+        <is>
+          <t>auto_now</t>
+        </is>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>수정 일시</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:J2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1815,20 +1785,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
     <col width="5" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="6" customWidth="1" min="7" max="7"/>
     <col width="8" customWidth="1" min="8" max="8"/>
     <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="60" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="46" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1838,10 +1807,10 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="30" customHeight="1">
+    <row r="2" ht="26" customHeight="1">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>요구사항정의서 헤더. 기획서당 생성.</t>
+          <t>요구사항정의서 헤더. 기획서당 생성. project FK 보유.</t>
         </is>
       </c>
     </row>
@@ -1894,11 +1863,6 @@
       <c r="J3" s="4" t="inlineStr">
         <is>
           <t>설명</t>
-        </is>
-      </c>
-      <c r="K3" s="4" t="inlineStr">
-        <is>
-          <t>비고</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1877,7 @@
       </c>
       <c r="C4" s="9" t="inlineStr">
         <is>
-          <t>bigint AI</t>
+          <t>bigint AUTO_INCREMENT</t>
         </is>
       </c>
       <c r="D4" s="10" t="inlineStr">
@@ -1928,10 +1892,9 @@
       <c r="I4" s="9" t="inlineStr"/>
       <c r="J4" s="5" t="inlineStr">
         <is>
-          <t>정의서 ID</t>
-        </is>
-      </c>
-      <c r="K4" s="5" t="inlineStr"/>
+          <t>ID</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="n">
@@ -1944,13 +1907,13 @@
       </c>
       <c r="C5" s="9" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr"/>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>spec_document</t>
+          <t>spec_document.spec_id</t>
         </is>
       </c>
       <c r="F5" s="8" t="inlineStr">
@@ -1966,7 +1929,6 @@
           <t>관련 기획서</t>
         </is>
       </c>
-      <c r="K5" s="5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="8" t="n">
@@ -1974,26 +1936,41 @@
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>project_id</t>
         </is>
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>varchar(200)</t>
+          <t>bigint</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr"/>
-      <c r="E6" s="8" t="inlineStr"/>
-      <c r="F6" s="8" t="inlineStr"/>
-      <c r="G6" s="8" t="inlineStr"/>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>project.id</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>SET NULL</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="H6" s="8" t="inlineStr"/>
-      <c r="I6" s="9" t="inlineStr"/>
+      <c r="I6" s="9" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J6" s="5" t="inlineStr">
         <is>
-          <t>요구사항 정의서 제목</t>
-        </is>
-      </c>
-      <c r="K6" s="5" t="inlineStr"/>
+          <t>소속 프로젝트</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="n">
@@ -2001,12 +1978,12 @@
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>version</t>
+          <t>title</t>
         </is>
       </c>
       <c r="C7" s="9" t="inlineStr">
         <is>
-          <t>varchar(20)</t>
+          <t>varchar(200)</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr"/>
@@ -2014,17 +1991,12 @@
       <c r="F7" s="8" t="inlineStr"/>
       <c r="G7" s="8" t="inlineStr"/>
       <c r="H7" s="8" t="inlineStr"/>
-      <c r="I7" s="9" t="inlineStr">
-        <is>
-          <t>v1.0</t>
-        </is>
-      </c>
+      <c r="I7" s="9" t="inlineStr"/>
       <c r="J7" s="5" t="inlineStr">
         <is>
-          <t>버전</t>
-        </is>
-      </c>
-      <c r="K7" s="5" t="inlineStr"/>
+          <t>요구사항 정의서 제목</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="8" t="n">
@@ -2032,30 +2004,29 @@
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>version</t>
         </is>
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>longtext</t>
+          <t>varchar(20)</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr"/>
       <c r="E8" s="8" t="inlineStr"/>
       <c r="F8" s="8" t="inlineStr"/>
-      <c r="G8" s="8" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="G8" s="8" t="inlineStr"/>
       <c r="H8" s="8" t="inlineStr"/>
-      <c r="I8" s="9" t="inlineStr"/>
+      <c r="I8" s="9" t="inlineStr">
+        <is>
+          <t>'v1.0'</t>
+        </is>
+      </c>
       <c r="J8" s="5" t="inlineStr">
         <is>
-          <t>설명</t>
-        </is>
-      </c>
-      <c r="K8" s="5" t="inlineStr"/>
+          <t>버전</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="n">
@@ -2063,25 +2034,17 @@
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>created_by_id</t>
+          <t>description</t>
         </is>
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>bigint</t>
+          <t>longtext</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr"/>
-      <c r="E9" s="8" t="inlineStr">
-        <is>
-          <t>user</t>
-        </is>
-      </c>
-      <c r="F9" s="8" t="inlineStr">
-        <is>
-          <t>SET NULL</t>
-        </is>
-      </c>
+      <c r="E9" s="8" t="inlineStr"/>
+      <c r="F9" s="8" t="inlineStr"/>
       <c r="G9" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -2091,10 +2054,9 @@
       <c r="I9" s="9" t="inlineStr"/>
       <c r="J9" s="5" t="inlineStr">
         <is>
-          <t>작성자</t>
-        </is>
-      </c>
-      <c r="K9" s="5" t="inlineStr"/>
+          <t>설명</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="n">
@@ -2102,30 +2064,41 @@
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>created_by_id</t>
         </is>
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>datetime(6)</t>
+          <t>bigint</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr"/>
-      <c r="E10" s="8" t="inlineStr"/>
-      <c r="F10" s="8" t="inlineStr"/>
-      <c r="G10" s="8" t="inlineStr"/>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>user.id</t>
+        </is>
+      </c>
+      <c r="F10" s="8" t="inlineStr">
+        <is>
+          <t>SET NULL</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="H10" s="8" t="inlineStr"/>
       <c r="I10" s="9" t="inlineStr">
         <is>
-          <t>now()</t>
+          <t>NULL</t>
         </is>
       </c>
       <c r="J10" s="5" t="inlineStr">
         <is>
-          <t>생성 일시</t>
-        </is>
-      </c>
-      <c r="K10" s="5" t="inlineStr"/>
+          <t>작성자</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="n">
@@ -2133,7 +2106,7 @@
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>updated_at</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
@@ -2148,20 +2121,49 @@
       <c r="H11" s="8" t="inlineStr"/>
       <c r="I11" s="9" t="inlineStr">
         <is>
-          <t>touch</t>
+          <t>now()</t>
         </is>
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
-          <t>수정 일시 (auto_now)</t>
-        </is>
-      </c>
-      <c r="K11" s="5" t="inlineStr"/>
+          <t>생성 일시</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>updated_at</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>datetime(6)</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr"/>
+      <c r="E12" s="8" t="inlineStr"/>
+      <c r="F12" s="8" t="inlineStr"/>
+      <c r="G12" s="8" t="inlineStr"/>
+      <c r="H12" s="8" t="inlineStr"/>
+      <c r="I12" s="9" t="inlineStr">
+        <is>
+          <t>auto_now</t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>수정 일시</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:J2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2173,20 +2175,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
     <col width="5" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="6" customWidth="1" min="7" max="7"/>
     <col width="8" customWidth="1" min="8" max="8"/>
     <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="60" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="46" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2196,10 +2197,10 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="30" customHeight="1">
+    <row r="2" ht="26" customHeight="1">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>요구사항 개별 항목. 업무배정(task_assignment)의 원천.</t>
+          <t>요구사항 개별 항목(REQ-xx). 업무배정의 원천. category_2 보유.</t>
         </is>
       </c>
     </row>
@@ -2252,11 +2253,6 @@
       <c r="J3" s="4" t="inlineStr">
         <is>
           <t>설명</t>
-        </is>
-      </c>
-      <c r="K3" s="4" t="inlineStr">
-        <is>
-          <t>비고</t>
         </is>
       </c>
     </row>
@@ -2271,7 +2267,7 @@
       </c>
       <c r="C4" s="9" t="inlineStr">
         <is>
-          <t>bigint AI</t>
+          <t>bigint AUTO_INCREMENT</t>
         </is>
       </c>
       <c r="D4" s="10" t="inlineStr">
@@ -2286,10 +2282,9 @@
       <c r="I4" s="9" t="inlineStr"/>
       <c r="J4" s="5" t="inlineStr">
         <is>
-          <t>항목 ID</t>
-        </is>
-      </c>
-      <c r="K4" s="5" t="inlineStr"/>
+          <t>ID</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="n">
@@ -2308,7 +2303,7 @@
       <c r="D5" s="8" t="inlineStr"/>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>requirement_definition</t>
+          <t>requirement_definition.id</t>
         </is>
       </c>
       <c r="F5" s="8" t="inlineStr">
@@ -2321,10 +2316,9 @@
       <c r="I5" s="9" t="inlineStr"/>
       <c r="J5" s="5" t="inlineStr">
         <is>
-          <t>소속 정의서</t>
-        </is>
-      </c>
-      <c r="K5" s="5" t="inlineStr"/>
+          <t>요구사항 정의서</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="8" t="n">
@@ -2351,7 +2345,6 @@
           <t>요구사항 코드 (예: REQ-01)</t>
         </is>
       </c>
-      <c r="K6" s="5" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="8" t="n">
@@ -2378,7 +2371,6 @@
           <t>요구사항명</t>
         </is>
       </c>
-      <c r="K7" s="5" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="8" t="n">
@@ -2405,7 +2397,6 @@
           <t>요구사항 상세 내용</t>
         </is>
       </c>
-      <c r="K8" s="5" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="8" t="n">
@@ -2424,7 +2415,7 @@
       <c r="D9" s="8" t="inlineStr"/>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>common_code</t>
+          <t>common_code.code_id</t>
         </is>
       </c>
       <c r="F9" s="8" t="inlineStr">
@@ -2438,13 +2429,16 @@
         </is>
       </c>
       <c r="H9" s="8" t="inlineStr"/>
-      <c r="I9" s="9" t="inlineStr"/>
+      <c r="I9" s="9" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J9" s="5" t="inlineStr">
         <is>
-          <t>우선순위 (HIGH / MEDIUM / LOW)</t>
-        </is>
-      </c>
-      <c r="K9" s="5" t="inlineStr"/>
+          <t>우선순위</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="n">
@@ -2472,10 +2466,9 @@
       <c r="I10" s="9" t="inlineStr"/>
       <c r="J10" s="5" t="inlineStr">
         <is>
-          <t>난이도 (상 / 중 / 하, 자유 문자열)</t>
-        </is>
-      </c>
-      <c r="K10" s="5" t="inlineStr"/>
+          <t>난이도 (상/중/하)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="n">
@@ -2506,12 +2499,41 @@
           <t>기능 카테고리</t>
         </is>
       </c>
-      <c r="K11" s="5" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>category_2</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>varchar(50)</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr"/>
+      <c r="E12" s="8" t="inlineStr"/>
+      <c r="F12" s="8" t="inlineStr"/>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H12" s="8" t="inlineStr"/>
+      <c r="I12" s="9" t="inlineStr"/>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>기능 카테고리 2</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:J2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2523,20 +2545,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K15"/>
+  <dimension ref="A1:J29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
     <col width="5" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="6" customWidth="1" min="7" max="7"/>
     <col width="8" customWidth="1" min="8" max="8"/>
     <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="60" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="46" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2546,10 +2567,10 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="30" customHeight="1">
+    <row r="2" ht="26" customHeight="1">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>요구사항 항목을 담당자에게 배정한 업무. 칸반보드가 이 테이블을 읽는다. 정렬: -created_at.</t>
+          <t>요구사항 항목을 담당자에게 배정한 업무(2026-09-07 컬럼 재설계).</t>
         </is>
       </c>
     </row>
@@ -2602,11 +2623,6 @@
       <c r="J3" s="4" t="inlineStr">
         <is>
           <t>설명</t>
-        </is>
-      </c>
-      <c r="K3" s="4" t="inlineStr">
-        <is>
-          <t>비고</t>
         </is>
       </c>
     </row>
@@ -2621,7 +2637,7 @@
       </c>
       <c r="C4" s="9" t="inlineStr">
         <is>
-          <t>bigint AI</t>
+          <t>bigint AUTO_INCREMENT</t>
         </is>
       </c>
       <c r="D4" s="10" t="inlineStr">
@@ -2636,10 +2652,9 @@
       <c r="I4" s="9" t="inlineStr"/>
       <c r="J4" s="5" t="inlineStr">
         <is>
-          <t>업무 ID</t>
-        </is>
-      </c>
-      <c r="K4" s="5" t="inlineStr"/>
+          <t>ID</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="n">
@@ -2647,34 +2662,33 @@
       </c>
       <c r="B5" s="9" t="inlineStr">
         <is>
-          <t>req_item_id</t>
+          <t>task_no</t>
         </is>
       </c>
       <c r="C5" s="9" t="inlineStr">
         <is>
-          <t>bigint</t>
+          <t>varchar(20)</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr"/>
-      <c r="E5" s="8" t="inlineStr">
-        <is>
-          <t>requirement_item</t>
-        </is>
-      </c>
-      <c r="F5" s="8" t="inlineStr">
-        <is>
-          <t>CASCADE</t>
-        </is>
-      </c>
-      <c r="G5" s="8" t="inlineStr"/>
-      <c r="H5" s="8" t="inlineStr"/>
+      <c r="E5" s="8" t="inlineStr"/>
+      <c r="F5" s="8" t="inlineStr"/>
+      <c r="G5" s="8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H5" s="8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I5" s="9" t="inlineStr"/>
       <c r="J5" s="5" t="inlineStr">
         <is>
-          <t>관련 요구사항 항목</t>
-        </is>
-      </c>
-      <c r="K5" s="5" t="inlineStr"/>
+          <t>업무배분 번호 (예: TASK-001)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="8" t="n">
@@ -2682,7 +2696,7 @@
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>assigned_user_id</t>
+          <t>req_item_id</t>
         </is>
       </c>
       <c r="C6" s="9" t="inlineStr">
@@ -2693,7 +2707,7 @@
       <c r="D6" s="8" t="inlineStr"/>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>user</t>
+          <t>requirement_item.id</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
@@ -2706,10 +2720,9 @@
       <c r="I6" s="9" t="inlineStr"/>
       <c r="J6" s="5" t="inlineStr">
         <is>
-          <t>담당자</t>
-        </is>
-      </c>
-      <c r="K6" s="5" t="inlineStr"/>
+          <t>관련 요구사항 항목</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="n">
@@ -2717,26 +2730,33 @@
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>task_title</t>
+          <t>assigned_user_id</t>
         </is>
       </c>
       <c r="C7" s="9" t="inlineStr">
         <is>
-          <t>varchar(200)</t>
+          <t>bigint</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr"/>
-      <c r="E7" s="8" t="inlineStr"/>
-      <c r="F7" s="8" t="inlineStr"/>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>user.id</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>CASCADE</t>
+        </is>
+      </c>
       <c r="G7" s="8" t="inlineStr"/>
       <c r="H7" s="8" t="inlineStr"/>
       <c r="I7" s="9" t="inlineStr"/>
       <c r="J7" s="5" t="inlineStr">
         <is>
-          <t>업무 제목</t>
-        </is>
-      </c>
-      <c r="K7" s="5" t="inlineStr"/>
+          <t>담당자</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="8" t="n">
@@ -2744,26 +2764,41 @@
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>task_description</t>
+          <t>project_id</t>
         </is>
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>longtext</t>
+          <t>bigint</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr"/>
-      <c r="E8" s="8" t="inlineStr"/>
-      <c r="F8" s="8" t="inlineStr"/>
-      <c r="G8" s="8" t="inlineStr"/>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>project.id</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>SET NULL</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="H8" s="8" t="inlineStr"/>
-      <c r="I8" s="9" t="inlineStr"/>
+      <c r="I8" s="9" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J8" s="5" t="inlineStr">
         <is>
-          <t>업무 상세 내용</t>
-        </is>
-      </c>
-      <c r="K8" s="5" t="inlineStr"/>
+          <t>프로젝트</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="n">
@@ -2771,12 +2806,12 @@
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>title</t>
         </is>
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>varchar(20)</t>
+          <t>varchar(200)</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr"/>
@@ -2786,15 +2821,14 @@
       <c r="H9" s="8" t="inlineStr"/>
       <c r="I9" s="9" t="inlineStr">
         <is>
-          <t>PENDING_APPROVAL</t>
+          <t>''</t>
         </is>
       </c>
       <c r="J9" s="5" t="inlineStr">
         <is>
-          <t>진행 / 승인 상태: PENDING_APPROVAL 승인 대기 / APPROVED 승인·알림 완료 / REJECTED 반려 / IN_PROGRESS 진행 중 / COMPLETED 완료</t>
-        </is>
-      </c>
-      <c r="K9" s="5" t="inlineStr"/>
+          <t>업무명</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="n">
@@ -2802,12 +2836,12 @@
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>start_date</t>
+          <t>description</t>
         </is>
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>longtext</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr"/>
@@ -2822,10 +2856,9 @@
       <c r="I10" s="9" t="inlineStr"/>
       <c r="J10" s="5" t="inlineStr">
         <is>
-          <t>시작 예정일</t>
-        </is>
-      </c>
-      <c r="K10" s="5" t="inlineStr"/>
+          <t>업무 상세 설명</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="n">
@@ -2833,12 +2866,12 @@
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>due_date</t>
+          <t>difficulty_reason</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>longtext</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr"/>
@@ -2853,10 +2886,9 @@
       <c r="I11" s="9" t="inlineStr"/>
       <c r="J11" s="5" t="inlineStr">
         <is>
-          <t>마감 예정일</t>
-        </is>
-      </c>
-      <c r="K11" s="5" t="inlineStr"/>
+          <t>난이도 판단 근거</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="8" t="n">
@@ -2864,30 +2896,29 @@
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>progress</t>
+          <t>estimated_hours</t>
         </is>
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>smallint UNSIGNED</t>
+          <t>double precision</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr"/>
       <c r="E12" s="8" t="inlineStr"/>
       <c r="F12" s="8" t="inlineStr"/>
-      <c r="G12" s="8" t="inlineStr"/>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="H12" s="8" t="inlineStr"/>
-      <c r="I12" s="9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="I12" s="9" t="inlineStr"/>
       <c r="J12" s="5" t="inlineStr">
         <is>
-          <t>진행률 (%) — 담당자가 직접 갱신</t>
-        </is>
-      </c>
-      <c r="K12" s="5" t="inlineStr"/>
+          <t>예상 소요 시간</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="8" t="n">
@@ -2895,7 +2926,7 @@
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>reject_reason</t>
+          <t>assignment_reason</t>
         </is>
       </c>
       <c r="C13" s="9" t="inlineStr">
@@ -2915,10 +2946,9 @@
       <c r="I13" s="9" t="inlineStr"/>
       <c r="J13" s="5" t="inlineStr">
         <is>
-          <t>반려 사유 (승인 대기 상태에서만 반려 가능)</t>
-        </is>
-      </c>
-      <c r="K13" s="5" t="inlineStr"/>
+          <t>배정 근거</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="n">
@@ -2926,30 +2956,29 @@
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>assigned_workload</t>
         </is>
       </c>
       <c r="C14" s="9" t="inlineStr">
         <is>
-          <t>datetime(6)</t>
+          <t>numeric(5, 2)</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr"/>
       <c r="E14" s="8" t="inlineStr"/>
       <c r="F14" s="8" t="inlineStr"/>
-      <c r="G14" s="8" t="inlineStr"/>
+      <c r="G14" s="8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="H14" s="8" t="inlineStr"/>
-      <c r="I14" s="9" t="inlineStr">
-        <is>
-          <t>now()</t>
-        </is>
-      </c>
+      <c r="I14" s="9" t="inlineStr"/>
       <c r="J14" s="5" t="inlineStr">
         <is>
-          <t>생성 일시</t>
-        </is>
-      </c>
-      <c r="K14" s="5" t="inlineStr"/>
+          <t>배정 시점 부하율</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="n">
@@ -2957,35 +2986,490 @@
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>updated_at</t>
+          <t>reject_reason</t>
         </is>
       </c>
       <c r="C15" s="9" t="inlineStr">
         <is>
-          <t>datetime(6)</t>
+          <t>varchar(500)</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr"/>
       <c r="E15" s="8" t="inlineStr"/>
       <c r="F15" s="8" t="inlineStr"/>
-      <c r="G15" s="8" t="inlineStr"/>
+      <c r="G15" s="8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="H15" s="8" t="inlineStr"/>
-      <c r="I15" s="9" t="inlineStr">
-        <is>
-          <t>touch</t>
-        </is>
-      </c>
+      <c r="I15" s="9" t="inlineStr"/>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t>수정 일시 (auto_now)</t>
-        </is>
-      </c>
-      <c r="K15" s="5" t="inlineStr"/>
+          <t>반려 사유</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>start_date</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr"/>
+      <c r="E16" s="8" t="inlineStr"/>
+      <c r="F16" s="8" t="inlineStr"/>
+      <c r="G16" s="8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H16" s="8" t="inlineStr"/>
+      <c r="I16" s="9" t="inlineStr"/>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>시작일</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>end_date</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="inlineStr"/>
+      <c r="E17" s="8" t="inlineStr"/>
+      <c r="F17" s="8" t="inlineStr"/>
+      <c r="G17" s="8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H17" s="8" t="inlineStr"/>
+      <c r="I17" s="9" t="inlineStr"/>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>종료 예정일</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>progress</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr"/>
+      <c r="E18" s="8" t="inlineStr"/>
+      <c r="F18" s="8" t="inlineStr"/>
+      <c r="G18" s="8" t="inlineStr"/>
+      <c r="H18" s="8" t="inlineStr"/>
+      <c r="I18" s="9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t>진행률(%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>linked_branch</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>varchar(200)</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="inlineStr"/>
+      <c r="E19" s="8" t="inlineStr"/>
+      <c r="F19" s="8" t="inlineStr"/>
+      <c r="G19" s="8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H19" s="8" t="inlineStr"/>
+      <c r="I19" s="9" t="inlineStr"/>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>연결 브랜치명</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="n">
+        <v>17</v>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>linked_pr_number</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="inlineStr"/>
+      <c r="E20" s="8" t="inlineStr"/>
+      <c r="F20" s="8" t="inlineStr"/>
+      <c r="G20" s="8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H20" s="8" t="inlineStr"/>
+      <c r="I20" s="9" t="inlineStr"/>
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>연결 PR 번호</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="n">
+        <v>18</v>
+      </c>
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>linked_pr_url</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>varchar(300)</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="inlineStr"/>
+      <c r="E21" s="8" t="inlineStr"/>
+      <c r="F21" s="8" t="inlineStr"/>
+      <c r="G21" s="8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H21" s="8" t="inlineStr"/>
+      <c r="I21" s="9" t="inlineStr"/>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>연결 PR 링크</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>status_code</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>varchar(50)</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="inlineStr"/>
+      <c r="E22" s="8" t="inlineStr">
+        <is>
+          <t>common_code.code_id</t>
+        </is>
+      </c>
+      <c r="F22" s="8" t="inlineStr">
+        <is>
+          <t>SET NULL</t>
+        </is>
+      </c>
+      <c r="G22" s="8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H22" s="8" t="inlineStr"/>
+      <c r="I22" s="9" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="J22" s="5" t="inlineStr">
+        <is>
+          <t>업무 상태 코드</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>difficulty_code</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>varchar(50)</t>
+        </is>
+      </c>
+      <c r="D23" s="8" t="inlineStr"/>
+      <c r="E23" s="8" t="inlineStr">
+        <is>
+          <t>common_code.code_id</t>
+        </is>
+      </c>
+      <c r="F23" s="8" t="inlineStr">
+        <is>
+          <t>SET NULL</t>
+        </is>
+      </c>
+      <c r="G23" s="8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H23" s="8" t="inlineStr"/>
+      <c r="I23" s="9" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>난이도 코드</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>git_status_code</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>varchar(50)</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="inlineStr"/>
+      <c r="E24" s="8" t="inlineStr">
+        <is>
+          <t>common_code.code_id</t>
+        </is>
+      </c>
+      <c r="F24" s="8" t="inlineStr">
+        <is>
+          <t>SET NULL</t>
+        </is>
+      </c>
+      <c r="G24" s="8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H24" s="8" t="inlineStr"/>
+      <c r="I24" s="9" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="J24" s="5" t="inlineStr">
+        <is>
+          <t>Git 연동 상태 코드</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="n">
+        <v>22</v>
+      </c>
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>parent_task_id</t>
+        </is>
+      </c>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>varchar(20)</t>
+        </is>
+      </c>
+      <c r="D25" s="8" t="inlineStr"/>
+      <c r="E25" s="8" t="inlineStr"/>
+      <c r="F25" s="8" t="inlineStr"/>
+      <c r="G25" s="8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H25" s="8" t="inlineStr"/>
+      <c r="I25" s="9" t="inlineStr"/>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>부모 업무 번호</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="8" t="n">
+        <v>23</v>
+      </c>
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t>epic_no</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>varchar(20)</t>
+        </is>
+      </c>
+      <c r="D26" s="8" t="inlineStr"/>
+      <c r="E26" s="8" t="inlineStr"/>
+      <c r="F26" s="8" t="inlineStr"/>
+      <c r="G26" s="8" t="inlineStr"/>
+      <c r="H26" s="8" t="inlineStr"/>
+      <c r="I26" s="9" t="inlineStr">
+        <is>
+          <t>''</t>
+        </is>
+      </c>
+      <c r="J26" s="5" t="inlineStr">
+        <is>
+          <t>epic ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="8" t="n">
+        <v>24</v>
+      </c>
+      <c r="B27" s="9" t="inlineStr">
+        <is>
+          <t>epic_title</t>
+        </is>
+      </c>
+      <c r="C27" s="9" t="inlineStr">
+        <is>
+          <t>varchar(200)</t>
+        </is>
+      </c>
+      <c r="D27" s="8" t="inlineStr"/>
+      <c r="E27" s="8" t="inlineStr"/>
+      <c r="F27" s="8" t="inlineStr"/>
+      <c r="G27" s="8" t="inlineStr"/>
+      <c r="H27" s="8" t="inlineStr"/>
+      <c r="I27" s="9" t="inlineStr">
+        <is>
+          <t>''</t>
+        </is>
+      </c>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>epic 제목</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="B28" s="9" t="inlineStr">
+        <is>
+          <t>created_at</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>datetime(6)</t>
+        </is>
+      </c>
+      <c r="D28" s="8" t="inlineStr"/>
+      <c r="E28" s="8" t="inlineStr"/>
+      <c r="F28" s="8" t="inlineStr"/>
+      <c r="G28" s="8" t="inlineStr"/>
+      <c r="H28" s="8" t="inlineStr"/>
+      <c r="I28" s="9" t="inlineStr">
+        <is>
+          <t>now()</t>
+        </is>
+      </c>
+      <c r="J28" s="5" t="inlineStr">
+        <is>
+          <t>생성 일시</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="B29" s="9" t="inlineStr">
+        <is>
+          <t>updated_at</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="inlineStr">
+        <is>
+          <t>datetime(6)</t>
+        </is>
+      </c>
+      <c r="D29" s="8" t="inlineStr"/>
+      <c r="E29" s="8" t="inlineStr"/>
+      <c r="F29" s="8" t="inlineStr"/>
+      <c r="G29" s="8" t="inlineStr"/>
+      <c r="H29" s="8" t="inlineStr"/>
+      <c r="I29" s="9" t="inlineStr">
+        <is>
+          <t>auto_now</t>
+        </is>
+      </c>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t>수정 일시</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:J2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2997,20 +3481,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
     <col width="5" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="6" customWidth="1" min="7" max="7"/>
     <col width="8" customWidth="1" min="8" max="8"/>
     <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="60" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="46" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3020,10 +3503,10 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="30" customHeight="1">
+    <row r="2" ht="26" customHeight="1">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>인앱 알림. 검토요청 / 승인 / 반려처럼 화면을 안 열면 모르는 이벤트를 통지. 정렬: -created_at.</t>
+          <t>인앱 알림. 검토요청/승인/반려 등 이벤트 통지.</t>
         </is>
       </c>
     </row>
@@ -3076,11 +3559,6 @@
       <c r="J3" s="4" t="inlineStr">
         <is>
           <t>설명</t>
-        </is>
-      </c>
-      <c r="K3" s="4" t="inlineStr">
-        <is>
-          <t>비고</t>
         </is>
       </c>
     </row>
@@ -3095,7 +3573,7 @@
       </c>
       <c r="C4" s="9" t="inlineStr">
         <is>
-          <t>bigint AI</t>
+          <t>bigint AUTO_INCREMENT</t>
         </is>
       </c>
       <c r="D4" s="10" t="inlineStr">
@@ -3110,10 +3588,9 @@
       <c r="I4" s="9" t="inlineStr"/>
       <c r="J4" s="5" t="inlineStr">
         <is>
-          <t>알림 ID</t>
-        </is>
-      </c>
-      <c r="K4" s="5" t="inlineStr"/>
+          <t>ID</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="n">
@@ -3132,7 +3609,7 @@
       <c r="D5" s="8" t="inlineStr"/>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>user</t>
+          <t>user.id</t>
         </is>
       </c>
       <c r="F5" s="8" t="inlineStr">
@@ -3148,7 +3625,6 @@
           <t>수신자</t>
         </is>
       </c>
-      <c r="K5" s="5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="8" t="n">
@@ -3175,7 +3651,6 @@
           <t>알림 메시지</t>
         </is>
       </c>
-      <c r="K6" s="5" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="8" t="n">
@@ -3198,15 +3673,14 @@
       <c r="H7" s="8" t="inlineStr"/>
       <c r="I7" s="9" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>Notification.NotificationType.INFO</t>
         </is>
       </c>
       <c r="J7" s="5" t="inlineStr">
         <is>
-          <t>알림 종류: info / success / warning / error</t>
-        </is>
-      </c>
-      <c r="K7" s="5" t="inlineStr"/>
+          <t>알림 종류  [info / success / warning / error]</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="8" t="n">
@@ -3234,10 +3708,9 @@
       <c r="I8" s="9" t="inlineStr"/>
       <c r="J8" s="5" t="inlineStr">
         <is>
-          <t>클릭 시 이동할 프론트 경로 (예: /documents?note=12)</t>
-        </is>
-      </c>
-      <c r="K8" s="5" t="inlineStr"/>
+          <t>이동 링크</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="n">
@@ -3250,7 +3723,7 @@
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>tinyint(1)</t>
+          <t>bool</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr"/>
@@ -3260,7 +3733,7 @@
       <c r="H9" s="8" t="inlineStr"/>
       <c r="I9" s="9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="J9" s="5" t="inlineStr">
@@ -3268,7 +3741,6 @@
           <t>읽음 여부</t>
         </is>
       </c>
-      <c r="K9" s="5" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="8" t="n">
@@ -3299,169 +3771,12 @@
           <t>생성 일시</t>
         </is>
       </c>
-      <c r="K10" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:J2"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="96" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>No.</t>
-        </is>
-      </c>
-      <c r="B1" s="4" t="inlineStr">
-        <is>
-          <t>항목</t>
-        </is>
-      </c>
-      <c r="C1" s="4" t="inlineStr">
-        <is>
-          <t>내용</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="5" t="inlineStr">
-        <is>
-          <t>구 필드 제거</t>
-        </is>
-      </c>
-      <c r="C2" s="5" t="inlineStr">
-        <is>
-          <t>spec_document.background, target_scope — 7섹션 템플릿 이전의 구 필드. 현재 미사용 → 제거 후보.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>기획서 섹션 구조화</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>spec_document의 7개 섹션이 전부 통짜 longtext. 노드 2는 섹션별 구조(content_html · items · features[] · is_incomplete)를 만드는데 DB엔 텍스트로 뭉개 저장. 구조 유지하려면 별도 spec_section 테이블 분리 고려.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>자유 텍스트 정규화</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>requirement_item.difficulty(상/중/하), user.past_projects(콤마 구분), meeting_note.attendees — 코드 테이블/관계로 정규화 후보.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>상태값 관리 방식 불일치</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>spec_document.status_code는 common_code FK인데 meeting_note.status / task_assignment.status / notification.type은 모델 내 TextChoices. 테이블마다 방식이 다름 → 통일 여부 결정.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>PK 타입 혼재</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>암시적 PK는 bigint(BigAutoField), meeting_id·spec_id·skill_id·cert_id만 int(AutoField). FK 타입도 int/bigint 혼재. 새 설계에서 PK 타입 일관성 결정.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>pipeline_history 사용 여부</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>스키마상 모든 단계를 로깅하게 돼 있으나, 실제로 views에서 write하는 경로가 있는지 확인 필요 (없으면 死 테이블).</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>meeting_note.project_id NULL 허용</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>'프로젝트 없는 회의록'이 존재 가능. 새 설계에서 필수(NOT NULL)로 할지 결정.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>export_db_spec 누락</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>export_db_spec.py의 TARGET_APPS에 notifications 누락 → 자동 생성 명세서에 notification 테이블이 빠져 있음.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3478,10 +3793,10 @@
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
     <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="56" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="52" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
     <col width="7" customWidth="1" min="8" max="8"/>
     <col width="8" customWidth="1" min="9" max="9"/>
   </cols>
@@ -3559,7 +3874,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>코드 대분류. 권한·우선순위·상태·부서·직급·기술·자격증 등 '코드 그룹'의 마스터.</t>
+          <t>코드 대분류(권한·우선순위·상태·부서·직급·기술·자격증 등)의 마스터.</t>
         </is>
       </c>
       <c r="G2" s="5" t="inlineStr">
@@ -3600,7 +3915,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>코드 상세값. 여러 테이블의 상태·분류·우선순위 컬럼이 이 테이블을 FK로 참조(enum을 DB로 분리). 정렬: group + sort_order.</t>
+          <t>코드 상세값. 여러 테이블의 상태·분류 컬럼이 이 테이블을 FK로 참조.</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
@@ -3636,12 +3951,12 @@
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>User (AbstractUser 확장)</t>
+          <t>User</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>로그인 계정 + 직원 정보. Django 기본 auth_user를 대체. 상단 11개 컬럼은 AbstractUser 상속분.</t>
+          <t>로그인 계정 + 직원 정보. Django 기본 auth_user 대체.</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
@@ -3650,10 +3965,10 @@
         </is>
       </c>
       <c r="H4" s="5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5">
@@ -3764,7 +4079,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>프로젝트 기본 정보. 회의록·이력이 여기에 소속된다.</t>
+          <t>프로젝트 기본 정보. 회의록·이력이 소속.</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
@@ -3805,7 +4120,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>프로젝트별 전체 타임라인 로그. 단계별로 한 행, 해당 산출물 FK와 작업자를 기록. 정렬: -created_at.</t>
+          <t>프로젝트별 전체 타임라인 로그(단계별 산출물 FK + 작업자).</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
@@ -3846,7 +4161,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>회의록 원문. AI 노드 1·2의 입력이자 상태(status) 관리 대상. 정렬: -created_at.</t>
+          <t>회의록 원문. AI 노드 1·2의 입력이자 상태 관리 대상.</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
@@ -3887,7 +4202,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>회의록당 생성되는 기획서 초안. 7개 섹션을 각각 한 덩어리 텍스트로 저장(행 단위 저장 안 함). 정렬: -created_at.</t>
+          <t>회의록당 생성되는 기획서 초안(7섹션 텍스트 + 섹션별 근거 evidence_data).</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
@@ -3899,7 +4214,7 @@
         <v>3</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11">
@@ -3928,7 +4243,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>요구사항정의서 헤더. 기획서당 생성.</t>
+          <t>요구사항정의서 헤더. 기획서당 생성. project FK 보유.</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
@@ -3937,10 +4252,10 @@
         </is>
       </c>
       <c r="H11" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12">
@@ -3969,7 +4284,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>요구사항 개별 항목. 업무배정(task_assignment)의 원천.</t>
+          <t>요구사항 개별 항목(REQ-xx). 업무배정의 원천. category_2 보유.</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
@@ -3981,7 +4296,7 @@
         <v>2</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13">
@@ -4010,7 +4325,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>요구사항 항목을 담당자에게 배정한 업무. 칸반보드가 이 테이블을 읽는다. 정렬: -created_at.</t>
+          <t>요구사항 항목을 담당자에게 배정한 업무(2026-09-07 컬럼 재설계).</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
@@ -4019,10 +4334,10 @@
         </is>
       </c>
       <c r="H13" s="5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="14">
@@ -4051,7 +4366,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>인앱 알림. 검토요청 / 승인 / 반려처럼 화면을 안 열면 모르는 이벤트를 통지. 정렬: -created_at.</t>
+          <t>인앱 알림. 검토요청/승인/반려 등 이벤트 통지.</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
@@ -4077,20 +4392,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
     <col width="5" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="6" customWidth="1" min="7" max="7"/>
     <col width="8" customWidth="1" min="8" max="8"/>
     <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="60" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="46" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4100,10 +4414,10 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="30" customHeight="1">
+    <row r="2" ht="26" customHeight="1">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>코드 대분류. 권한·우선순위·상태·부서·직급·기술·자격증 등 '코드 그룹'의 마스터.</t>
+          <t>코드 대분류(권한·우선순위·상태·부서·직급·기술·자격증 등)의 마스터.</t>
         </is>
       </c>
     </row>
@@ -4156,11 +4470,6 @@
       <c r="J3" s="4" t="inlineStr">
         <is>
           <t>설명</t>
-        </is>
-      </c>
-      <c r="K3" s="4" t="inlineStr">
-        <is>
-          <t>비고</t>
         </is>
       </c>
     </row>
@@ -4190,10 +4499,9 @@
       <c r="I4" s="9" t="inlineStr"/>
       <c r="J4" s="5" t="inlineStr">
         <is>
-          <t>코드 그룹 ID (예: USER_ROLE)</t>
-        </is>
-      </c>
-      <c r="K4" s="5" t="inlineStr"/>
+          <t>코드 그룹 ID</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="n">
@@ -4220,7 +4528,6 @@
           <t>코드 그룹명</t>
         </is>
       </c>
-      <c r="K5" s="5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="8" t="n">
@@ -4251,7 +4558,6 @@
           <t>설명</t>
         </is>
       </c>
-      <c r="K6" s="5" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="8" t="n">
@@ -4264,7 +4570,7 @@
       </c>
       <c r="C7" s="9" t="inlineStr">
         <is>
-          <t>tinyint(1)</t>
+          <t>bool</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr"/>
@@ -4274,7 +4580,7 @@
       <c r="H7" s="8" t="inlineStr"/>
       <c r="I7" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>True</t>
         </is>
       </c>
       <c r="J7" s="5" t="inlineStr">
@@ -4282,7 +4588,6 @@
           <t>사용 여부</t>
         </is>
       </c>
-      <c r="K7" s="5" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="8" t="n">
@@ -4313,12 +4618,11 @@
           <t>생성 일시</t>
         </is>
       </c>
-      <c r="K8" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:J2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4330,20 +4634,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
     <col width="5" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="6" customWidth="1" min="7" max="7"/>
     <col width="8" customWidth="1" min="8" max="8"/>
     <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="60" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="46" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4353,10 +4656,10 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="30" customHeight="1">
+    <row r="2" ht="26" customHeight="1">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>코드 상세값. 여러 테이블의 상태·분류·우선순위 컬럼이 이 테이블을 FK로 참조(enum을 DB로 분리). 정렬: group + sort_order.</t>
+          <t>코드 상세값. 여러 테이블의 상태·분류 컬럼이 이 테이블을 FK로 참조.</t>
         </is>
       </c>
     </row>
@@ -4409,11 +4712,6 @@
       <c r="J3" s="4" t="inlineStr">
         <is>
           <t>설명</t>
-        </is>
-      </c>
-      <c r="K3" s="4" t="inlineStr">
-        <is>
-          <t>비고</t>
         </is>
       </c>
     </row>
@@ -4443,10 +4741,9 @@
       <c r="I4" s="9" t="inlineStr"/>
       <c r="J4" s="5" t="inlineStr">
         <is>
-          <t>코드 ID (예: HIGH)</t>
-        </is>
-      </c>
-      <c r="K4" s="5" t="inlineStr"/>
+          <t>코드 ID</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="n">
@@ -4465,7 +4762,7 @@
       <c r="D5" s="8" t="inlineStr"/>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>common_code_group</t>
+          <t>common_code_group.group_code</t>
         </is>
       </c>
       <c r="F5" s="8" t="inlineStr">
@@ -4478,10 +4775,9 @@
       <c r="I5" s="9" t="inlineStr"/>
       <c r="J5" s="5" t="inlineStr">
         <is>
-          <t>소속 코드 그룹</t>
-        </is>
-      </c>
-      <c r="K5" s="5" t="inlineStr"/>
+          <t>코드 그룹</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="8" t="n">
@@ -4505,10 +4801,9 @@
       <c r="I6" s="9" t="inlineStr"/>
       <c r="J6" s="5" t="inlineStr">
         <is>
-          <t>코드명 (화면 표시값)</t>
-        </is>
-      </c>
-      <c r="K6" s="5" t="inlineStr"/>
+          <t>코드명</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="n">
@@ -4521,7 +4816,7 @@
       </c>
       <c r="C7" s="9" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr"/>
@@ -4539,7 +4834,6 @@
           <t>정렬 순서</t>
         </is>
       </c>
-      <c r="K7" s="5" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="8" t="n">
@@ -4552,7 +4846,7 @@
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>tinyint(1)</t>
+          <t>bool</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr"/>
@@ -4562,7 +4856,7 @@
       <c r="H8" s="8" t="inlineStr"/>
       <c r="I8" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>True</t>
         </is>
       </c>
       <c r="J8" s="5" t="inlineStr">
@@ -4570,7 +4864,6 @@
           <t>사용 여부</t>
         </is>
       </c>
-      <c r="K8" s="5" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="8" t="n">
@@ -4601,7 +4894,6 @@
           <t>설명</t>
         </is>
       </c>
-      <c r="K9" s="5" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="8" t="n">
@@ -4632,12 +4924,11 @@
           <t>생성 일시</t>
         </is>
       </c>
-      <c r="K10" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:J2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4649,33 +4940,32 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K25"/>
+  <dimension ref="A1:J27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
     <col width="5" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="6" customWidth="1" min="7" max="7"/>
     <col width="8" customWidth="1" min="8" max="8"/>
     <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="60" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="46" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>user  (사용자)   ·   User (AbstractUser 확장)   ·   앱: users</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="30" customHeight="1">
+          <t>user  (사용자)   ·   User   ·   앱: users</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="26" customHeight="1">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>로그인 계정 + 직원 정보. Django 기본 auth_user를 대체. 상단 11개 컬럼은 AbstractUser 상속분.</t>
+          <t>로그인 계정 + 직원 정보. Django 기본 auth_user 대체.</t>
         </is>
       </c>
     </row>
@@ -4728,11 +5018,6 @@
       <c r="J3" s="4" t="inlineStr">
         <is>
           <t>설명</t>
-        </is>
-      </c>
-      <c r="K3" s="4" t="inlineStr">
-        <is>
-          <t>비고</t>
         </is>
       </c>
     </row>
@@ -4747,7 +5032,7 @@
       </c>
       <c r="C4" s="9" t="inlineStr">
         <is>
-          <t>bigint AI</t>
+          <t>bigint AUTO_INCREMENT</t>
         </is>
       </c>
       <c r="D4" s="10" t="inlineStr">
@@ -4762,10 +5047,9 @@
       <c r="I4" s="9" t="inlineStr"/>
       <c r="J4" s="5" t="inlineStr">
         <is>
-          <t>내부 식별자</t>
-        </is>
-      </c>
-      <c r="K4" s="5" t="inlineStr"/>
+          <t>ID</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="n">
@@ -4789,10 +5073,9 @@
       <c r="I5" s="9" t="inlineStr"/>
       <c r="J5" s="5" t="inlineStr">
         <is>
-          <t>해시된 비밀번호 (상속)</t>
-        </is>
-      </c>
-      <c r="K5" s="5" t="inlineStr"/>
+          <t>비밀번호</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="8" t="n">
@@ -4820,10 +5103,9 @@
       <c r="I6" s="9" t="inlineStr"/>
       <c r="J6" s="5" t="inlineStr">
         <is>
-          <t>마지막 로그인 (상속)</t>
-        </is>
-      </c>
-      <c r="K6" s="5" t="inlineStr"/>
+          <t>마지막 로그인</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="n">
@@ -4836,7 +5118,7 @@
       </c>
       <c r="C7" s="9" t="inlineStr">
         <is>
-          <t>tinyint(1)</t>
+          <t>bool</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr"/>
@@ -4846,15 +5128,14 @@
       <c r="H7" s="8" t="inlineStr"/>
       <c r="I7" s="9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="J7" s="5" t="inlineStr">
         <is>
-          <t>슈퍼유저 여부 (상속)</t>
-        </is>
-      </c>
-      <c r="K7" s="5" t="inlineStr"/>
+          <t>최상위 사용자 권한</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="8" t="n">
@@ -4882,10 +5163,9 @@
       <c r="I8" s="9" t="inlineStr"/>
       <c r="J8" s="5" t="inlineStr">
         <is>
-          <t>로그인 ID (상속)</t>
-        </is>
-      </c>
-      <c r="K8" s="5" t="inlineStr"/>
+          <t>사용자 이름</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="n">
@@ -4906,17 +5186,12 @@
       <c r="F9" s="8" t="inlineStr"/>
       <c r="G9" s="8" t="inlineStr"/>
       <c r="H9" s="8" t="inlineStr"/>
-      <c r="I9" s="9" t="inlineStr">
-        <is>
-          <t>''</t>
-        </is>
-      </c>
+      <c r="I9" s="9" t="inlineStr"/>
       <c r="J9" s="5" t="inlineStr">
         <is>
-          <t>이름 (상속)</t>
-        </is>
-      </c>
-      <c r="K9" s="5" t="inlineStr"/>
+          <t>이름</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="n">
@@ -4937,17 +5212,12 @@
       <c r="F10" s="8" t="inlineStr"/>
       <c r="G10" s="8" t="inlineStr"/>
       <c r="H10" s="8" t="inlineStr"/>
-      <c r="I10" s="9" t="inlineStr">
-        <is>
-          <t>''</t>
-        </is>
-      </c>
+      <c r="I10" s="9" t="inlineStr"/>
       <c r="J10" s="5" t="inlineStr">
         <is>
-          <t>성 (상속)</t>
-        </is>
-      </c>
-      <c r="K10" s="5" t="inlineStr"/>
+          <t>성</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="n">
@@ -4968,17 +5238,12 @@
       <c r="F11" s="8" t="inlineStr"/>
       <c r="G11" s="8" t="inlineStr"/>
       <c r="H11" s="8" t="inlineStr"/>
-      <c r="I11" s="9" t="inlineStr">
-        <is>
-          <t>''</t>
-        </is>
-      </c>
+      <c r="I11" s="9" t="inlineStr"/>
       <c r="J11" s="5" t="inlineStr">
         <is>
-          <t>이메일 (상속)</t>
-        </is>
-      </c>
-      <c r="K11" s="5" t="inlineStr"/>
+          <t>이메일 주소</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="8" t="n">
@@ -4991,7 +5256,7 @@
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>tinyint(1)</t>
+          <t>bool</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr"/>
@@ -5001,15 +5266,14 @@
       <c r="H12" s="8" t="inlineStr"/>
       <c r="I12" s="9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="J12" s="5" t="inlineStr">
         <is>
-          <t>admin 접근 여부 (상속)</t>
-        </is>
-      </c>
-      <c r="K12" s="5" t="inlineStr"/>
+          <t>스태프 권한</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="8" t="n">
@@ -5022,7 +5286,7 @@
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>tinyint(1)</t>
+          <t>bool</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr"/>
@@ -5032,15 +5296,14 @@
       <c r="H13" s="8" t="inlineStr"/>
       <c r="I13" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>True</t>
         </is>
       </c>
       <c r="J13" s="5" t="inlineStr">
         <is>
-          <t>계정 활성 여부 (상속)</t>
-        </is>
-      </c>
-      <c r="K13" s="5" t="inlineStr"/>
+          <t>활성</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="n">
@@ -5063,15 +5326,14 @@
       <c r="H14" s="8" t="inlineStr"/>
       <c r="I14" s="9" t="inlineStr">
         <is>
-          <t>now()</t>
+          <t>now</t>
         </is>
       </c>
       <c r="J14" s="5" t="inlineStr">
         <is>
-          <t>가입 일시 (상속)</t>
-        </is>
-      </c>
-      <c r="K14" s="5" t="inlineStr"/>
+          <t>등록일</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="n">
@@ -5106,7 +5368,6 @@
           <t>사원번호</t>
         </is>
       </c>
-      <c r="K15" s="5" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="8" t="n">
@@ -5137,7 +5398,6 @@
           <t>전화번호</t>
         </is>
       </c>
-      <c r="K16" s="5" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="8" t="n">
@@ -5156,7 +5416,7 @@
       <c r="D17" s="8" t="inlineStr"/>
       <c r="E17" s="8" t="inlineStr">
         <is>
-          <t>common_code</t>
+          <t>common_code.code_id</t>
         </is>
       </c>
       <c r="F17" s="8" t="inlineStr">
@@ -5170,13 +5430,16 @@
         </is>
       </c>
       <c r="H17" s="8" t="inlineStr"/>
-      <c r="I17" s="9" t="inlineStr"/>
+      <c r="I17" s="9" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
           <t>부서 코드</t>
         </is>
       </c>
-      <c r="K17" s="5" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="8" t="n">
@@ -5195,7 +5458,7 @@
       <c r="D18" s="8" t="inlineStr"/>
       <c r="E18" s="8" t="inlineStr">
         <is>
-          <t>common_code</t>
+          <t>common_code.code_id</t>
         </is>
       </c>
       <c r="F18" s="8" t="inlineStr">
@@ -5209,13 +5472,16 @@
         </is>
       </c>
       <c r="H18" s="8" t="inlineStr"/>
-      <c r="I18" s="9" t="inlineStr"/>
+      <c r="I18" s="9" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J18" s="5" t="inlineStr">
         <is>
           <t>직무 코드</t>
         </is>
       </c>
-      <c r="K18" s="5" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="8" t="n">
@@ -5234,7 +5500,7 @@
       <c r="D19" s="8" t="inlineStr"/>
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t>common_code</t>
+          <t>common_code.code_id</t>
         </is>
       </c>
       <c r="F19" s="8" t="inlineStr">
@@ -5248,13 +5514,16 @@
         </is>
       </c>
       <c r="H19" s="8" t="inlineStr"/>
-      <c r="I19" s="9" t="inlineStr"/>
+      <c r="I19" s="9" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J19" s="5" t="inlineStr">
         <is>
           <t>직급 코드</t>
         </is>
       </c>
-      <c r="K19" s="5" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="8" t="n">
@@ -5273,7 +5542,7 @@
       <c r="D20" s="8" t="inlineStr"/>
       <c r="E20" s="8" t="inlineStr">
         <is>
-          <t>common_code</t>
+          <t>common_code.code_id</t>
         </is>
       </c>
       <c r="F20" s="8" t="inlineStr">
@@ -5287,13 +5556,16 @@
         </is>
       </c>
       <c r="H20" s="8" t="inlineStr"/>
-      <c r="I20" s="9" t="inlineStr"/>
+      <c r="I20" s="9" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J20" s="5" t="inlineStr">
         <is>
           <t>권한 코드</t>
         </is>
       </c>
-      <c r="K20" s="5" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="8" t="n">
@@ -5312,7 +5584,7 @@
       <c r="D21" s="8" t="inlineStr"/>
       <c r="E21" s="8" t="inlineStr">
         <is>
-          <t>common_code</t>
+          <t>common_code.code_id</t>
         </is>
       </c>
       <c r="F21" s="8" t="inlineStr">
@@ -5326,13 +5598,16 @@
         </is>
       </c>
       <c r="H21" s="8" t="inlineStr"/>
-      <c r="I21" s="9" t="inlineStr"/>
+      <c r="I21" s="9" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J21" s="5" t="inlineStr">
         <is>
           <t>상태 코드</t>
         </is>
       </c>
-      <c r="K21" s="5" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="8" t="n">
@@ -5345,7 +5620,7 @@
       </c>
       <c r="C22" s="9" t="inlineStr">
         <is>
-          <t>tinyint(1)</t>
+          <t>bool</t>
         </is>
       </c>
       <c r="D22" s="8" t="inlineStr"/>
@@ -5355,15 +5630,14 @@
       <c r="H22" s="8" t="inlineStr"/>
       <c r="I22" s="9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="J22" s="5" t="inlineStr">
         <is>
-          <t>현재 업무 진행 중 여부</t>
-        </is>
-      </c>
-      <c r="K22" s="5" t="inlineStr"/>
+          <t>현재 작업 중 여부</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="8" t="n">
@@ -5394,7 +5668,6 @@
           <t>입사일</t>
         </is>
       </c>
-      <c r="K23" s="5" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="8" t="n">
@@ -5425,7 +5698,6 @@
           <t>퇴사일</t>
         </is>
       </c>
-      <c r="K24" s="5" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="8" t="n">
@@ -5453,15 +5725,66 @@
       <c r="I25" s="9" t="inlineStr"/>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>참여 프로젝트 이력 (콤마 구분 자유 텍스트)</t>
-        </is>
-      </c>
-      <c r="K25" s="5" t="inlineStr"/>
+          <t>참여 프로젝트 이력(콤마 구분)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="8" t="n">
+        <v>23</v>
+      </c>
+      <c r="B26" s="9" t="n"/>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>M2M</t>
+        </is>
+      </c>
+      <c r="D26" s="8" t="inlineStr"/>
+      <c r="E26" s="8" t="inlineStr">
+        <is>
+          <t>auth_group.id</t>
+        </is>
+      </c>
+      <c r="F26" s="8" t="inlineStr"/>
+      <c r="G26" s="8" t="inlineStr"/>
+      <c r="H26" s="8" t="inlineStr"/>
+      <c r="I26" s="9" t="inlineStr"/>
+      <c r="J26" s="5" t="inlineStr">
+        <is>
+          <t>그룹</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="8" t="n">
+        <v>24</v>
+      </c>
+      <c r="B27" s="9" t="n"/>
+      <c r="C27" s="9" t="inlineStr">
+        <is>
+          <t>M2M</t>
+        </is>
+      </c>
+      <c r="D27" s="8" t="inlineStr"/>
+      <c r="E27" s="8" t="inlineStr">
+        <is>
+          <t>auth_permission.id</t>
+        </is>
+      </c>
+      <c r="F27" s="8" t="inlineStr"/>
+      <c r="G27" s="8" t="inlineStr"/>
+      <c r="H27" s="8" t="inlineStr"/>
+      <c r="I27" s="9" t="inlineStr"/>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>사용자 권한</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:J2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5473,20 +5796,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
     <col width="5" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="6" customWidth="1" min="7" max="7"/>
     <col width="8" customWidth="1" min="8" max="8"/>
     <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="60" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="46" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5496,7 +5818,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="30" customHeight="1">
+    <row r="2" ht="26" customHeight="1">
       <c r="A2" s="7" t="inlineStr">
         <is>
           <t>사용자별 보유 기술 스택 + 숙련도.</t>
@@ -5552,11 +5874,6 @@
       <c r="J3" s="4" t="inlineStr">
         <is>
           <t>설명</t>
-        </is>
-      </c>
-      <c r="K3" s="4" t="inlineStr">
-        <is>
-          <t>비고</t>
         </is>
       </c>
     </row>
@@ -5571,7 +5888,7 @@
       </c>
       <c r="C4" s="9" t="inlineStr">
         <is>
-          <t>int AI</t>
+          <t>integer AUTO_INCREMENT</t>
         </is>
       </c>
       <c r="D4" s="10" t="inlineStr">
@@ -5589,7 +5906,6 @@
           <t>기술 ID</t>
         </is>
       </c>
-      <c r="K4" s="5" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="8" t="n">
@@ -5608,7 +5924,7 @@
       <c r="D5" s="8" t="inlineStr"/>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>user</t>
+          <t>user.id</t>
         </is>
       </c>
       <c r="F5" s="8" t="inlineStr">
@@ -5624,7 +5940,6 @@
           <t>사용자</t>
         </is>
       </c>
-      <c r="K5" s="5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="8" t="n">
@@ -5643,7 +5958,7 @@
       <c r="D6" s="8" t="inlineStr"/>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>common_code</t>
+          <t>common_code.code_id</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
@@ -5659,7 +5974,6 @@
           <t>기술 코드</t>
         </is>
       </c>
-      <c r="K6" s="5" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="8" t="n">
@@ -5672,7 +5986,7 @@
       </c>
       <c r="C7" s="9" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr"/>
@@ -5690,12 +6004,11 @@
           <t>숙련도 (1~5)</t>
         </is>
       </c>
-      <c r="K7" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:J2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5707,20 +6020,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
     <col width="5" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="6" customWidth="1" min="7" max="7"/>
     <col width="8" customWidth="1" min="8" max="8"/>
     <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="60" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="46" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5730,7 +6042,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="30" customHeight="1">
+    <row r="2" ht="26" customHeight="1">
       <c r="A2" s="7" t="inlineStr">
         <is>
           <t>사용자별 보유 자격증 + 취득일.</t>
@@ -5786,11 +6098,6 @@
       <c r="J3" s="4" t="inlineStr">
         <is>
           <t>설명</t>
-        </is>
-      </c>
-      <c r="K3" s="4" t="inlineStr">
-        <is>
-          <t>비고</t>
         </is>
       </c>
     </row>
@@ -5805,7 +6112,7 @@
       </c>
       <c r="C4" s="9" t="inlineStr">
         <is>
-          <t>int AI</t>
+          <t>integer AUTO_INCREMENT</t>
         </is>
       </c>
       <c r="D4" s="10" t="inlineStr">
@@ -5823,7 +6130,6 @@
           <t>자격증 ID</t>
         </is>
       </c>
-      <c r="K4" s="5" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="8" t="n">
@@ -5842,7 +6148,7 @@
       <c r="D5" s="8" t="inlineStr"/>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>user</t>
+          <t>user.id</t>
         </is>
       </c>
       <c r="F5" s="8" t="inlineStr">
@@ -5858,7 +6164,6 @@
           <t>사용자</t>
         </is>
       </c>
-      <c r="K5" s="5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="8" t="n">
@@ -5877,7 +6182,7 @@
       <c r="D6" s="8" t="inlineStr"/>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>common_code</t>
+          <t>common_code.code_id</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
@@ -5893,7 +6198,6 @@
           <t>자격증 코드</t>
         </is>
       </c>
-      <c r="K6" s="5" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="8" t="n">
@@ -5924,12 +6228,11 @@
           <t>취득일</t>
         </is>
       </c>
-      <c r="K7" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:J2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5941,20 +6244,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
     <col width="5" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="6" customWidth="1" min="7" max="7"/>
     <col width="8" customWidth="1" min="8" max="8"/>
     <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="60" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="46" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5964,10 +6266,10 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="30" customHeight="1">
+    <row r="2" ht="26" customHeight="1">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>프로젝트 기본 정보. 회의록·이력이 여기에 소속된다.</t>
+          <t>프로젝트 기본 정보. 회의록·이력이 소속.</t>
         </is>
       </c>
     </row>
@@ -6020,11 +6322,6 @@
       <c r="J3" s="4" t="inlineStr">
         <is>
           <t>설명</t>
-        </is>
-      </c>
-      <c r="K3" s="4" t="inlineStr">
-        <is>
-          <t>비고</t>
         </is>
       </c>
     </row>
@@ -6039,7 +6336,7 @@
       </c>
       <c r="C4" s="9" t="inlineStr">
         <is>
-          <t>bigint AI</t>
+          <t>bigint AUTO_INCREMENT</t>
         </is>
       </c>
       <c r="D4" s="10" t="inlineStr">
@@ -6054,10 +6351,9 @@
       <c r="I4" s="9" t="inlineStr"/>
       <c r="J4" s="5" t="inlineStr">
         <is>
-          <t>프로젝트 ID</t>
-        </is>
-      </c>
-      <c r="K4" s="5" t="inlineStr"/>
+          <t>ID</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="n">
@@ -6084,7 +6380,6 @@
           <t>프로젝트명</t>
         </is>
       </c>
-      <c r="K5" s="5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="8" t="n">
@@ -6115,7 +6410,6 @@
           <t>프로젝트 설명</t>
         </is>
       </c>
-      <c r="K6" s="5" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="8" t="n">
@@ -6134,7 +6428,7 @@
       <c r="D7" s="8" t="inlineStr"/>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>user</t>
+          <t>user.id</t>
         </is>
       </c>
       <c r="F7" s="8" t="inlineStr">
@@ -6148,13 +6442,16 @@
         </is>
       </c>
       <c r="H7" s="8" t="inlineStr"/>
-      <c r="I7" s="9" t="inlineStr"/>
+      <c r="I7" s="9" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J7" s="5" t="inlineStr">
         <is>
           <t>프로젝트 관리자</t>
         </is>
       </c>
-      <c r="K7" s="5" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="8" t="n">
@@ -6185,7 +6482,6 @@
           <t>생성 일시</t>
         </is>
       </c>
-      <c r="K8" s="5" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="8" t="n">
@@ -6208,20 +6504,19 @@
       <c r="H9" s="8" t="inlineStr"/>
       <c r="I9" s="9" t="inlineStr">
         <is>
-          <t>touch</t>
+          <t>auto_now</t>
         </is>
       </c>
       <c r="J9" s="5" t="inlineStr">
         <is>
-          <t>수정 일시 (auto_now)</t>
-        </is>
-      </c>
-      <c r="K9" s="5" t="inlineStr"/>
+          <t>수정 일시</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:J2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6233,20 +6528,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
     <col width="5" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="6" customWidth="1" min="7" max="7"/>
     <col width="8" customWidth="1" min="8" max="8"/>
     <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="60" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="46" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6256,10 +6550,10 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="30" customHeight="1">
+    <row r="2" ht="26" customHeight="1">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>프로젝트별 전체 타임라인 로그. 단계별로 한 행, 해당 산출물 FK와 작업자를 기록. 정렬: -created_at.</t>
+          <t>프로젝트별 전체 타임라인 로그(단계별 산출물 FK + 작업자).</t>
         </is>
       </c>
     </row>
@@ -6312,11 +6606,6 @@
       <c r="J3" s="4" t="inlineStr">
         <is>
           <t>설명</t>
-        </is>
-      </c>
-      <c r="K3" s="4" t="inlineStr">
-        <is>
-          <t>비고</t>
         </is>
       </c>
     </row>
@@ -6331,7 +6620,7 @@
       </c>
       <c r="C4" s="9" t="inlineStr">
         <is>
-          <t>bigint AI</t>
+          <t>bigint AUTO_INCREMENT</t>
         </is>
       </c>
       <c r="D4" s="10" t="inlineStr">
@@ -6346,10 +6635,9 @@
       <c r="I4" s="9" t="inlineStr"/>
       <c r="J4" s="5" t="inlineStr">
         <is>
-          <t>이력 ID</t>
-        </is>
-      </c>
-      <c r="K4" s="5" t="inlineStr"/>
+          <t>ID</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="n">
@@ -6368,7 +6656,7 @@
       <c r="D5" s="8" t="inlineStr"/>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>project</t>
+          <t>project.id</t>
         </is>
       </c>
       <c r="F5" s="8" t="inlineStr">
@@ -6384,7 +6672,6 @@
           <t>프로젝트</t>
         </is>
       </c>
-      <c r="K5" s="5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="8" t="n">
@@ -6397,13 +6684,13 @@
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr"/>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>meeting_note</t>
+          <t>meeting_note.meeting_id</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
@@ -6417,13 +6704,16 @@
         </is>
       </c>
       <c r="H6" s="8" t="inlineStr"/>
-      <c r="I6" s="9" t="inlineStr"/>
+      <c r="I6" s="9" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J6" s="5" t="inlineStr">
         <is>
           <t>관련 회의록</t>
         </is>
       </c>
-      <c r="K6" s="5" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="8" t="n">
@@ -6436,13 +6726,13 @@
       </c>
       <c r="C7" s="9" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr"/>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>spec_document</t>
+          <t>spec_document.spec_id</t>
         </is>
       </c>
       <c r="F7" s="8" t="inlineStr">
@@ -6456,13 +6746,16 @@
         </is>
       </c>
       <c r="H7" s="8" t="inlineStr"/>
-      <c r="I7" s="9" t="inlineStr"/>
+      <c r="I7" s="9" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J7" s="5" t="inlineStr">
         <is>
           <t>관련 기획서</t>
         </is>
       </c>
-      <c r="K7" s="5" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="8" t="n">
@@ -6481,7 +6774,7 @@
       <c r="D8" s="8" t="inlineStr"/>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>requirement_definition</t>
+          <t>requirement_definition.id</t>
         </is>
       </c>
       <c r="F8" s="8" t="inlineStr">
@@ -6495,13 +6788,16 @@
         </is>
       </c>
       <c r="H8" s="8" t="inlineStr"/>
-      <c r="I8" s="9" t="inlineStr"/>
+      <c r="I8" s="9" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J8" s="5" t="inlineStr">
         <is>
           <t>관련 요구사항정의서</t>
         </is>
       </c>
-      <c r="K8" s="5" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="8" t="n">
@@ -6520,7 +6816,7 @@
       <c r="D9" s="8" t="inlineStr"/>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>task_assignment</t>
+          <t>task_assignment.id</t>
         </is>
       </c>
       <c r="F9" s="8" t="inlineStr">
@@ -6534,13 +6830,16 @@
         </is>
       </c>
       <c r="H9" s="8" t="inlineStr"/>
-      <c r="I9" s="9" t="inlineStr"/>
+      <c r="I9" s="9" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J9" s="5" t="inlineStr">
         <is>
           <t>관련 업무</t>
         </is>
       </c>
-      <c r="K9" s="5" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="8" t="n">
@@ -6564,10 +6863,9 @@
       <c r="I10" s="9" t="inlineStr"/>
       <c r="J10" s="5" t="inlineStr">
         <is>
-          <t>파이프라인 단계: MEETING_REGISTERED / SPEC_GENERATED / REQ_DEFINED / TASK_ASSIGNED / TASK_IN_PROGRESS / COMPLETED</t>
-        </is>
-      </c>
-      <c r="K10" s="5" t="inlineStr"/>
+          <t>파이프라인 단계  [MEETING_REGISTERED / SPEC_GENERATED / REQ_DEFINED / TASK_ASSIGNED / TASK_IN_PROGRESS / COMPLETED]</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="n">
@@ -6594,7 +6892,6 @@
           <t>이력 요약 타이틀</t>
         </is>
       </c>
-      <c r="K11" s="5" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="8" t="n">
@@ -6622,10 +6919,9 @@
       <c r="I12" s="9" t="inlineStr"/>
       <c r="J12" s="5" t="inlineStr">
         <is>
-          <t>상세 변경 내용 / 로그</t>
-        </is>
-      </c>
-      <c r="K12" s="5" t="inlineStr"/>
+          <t>상세 변경 내용/로그</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="8" t="n">
@@ -6644,7 +6940,7 @@
       <c r="D13" s="8" t="inlineStr"/>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t>user</t>
+          <t>user.id</t>
         </is>
       </c>
       <c r="F13" s="8" t="inlineStr">
@@ -6658,13 +6954,16 @@
         </is>
       </c>
       <c r="H13" s="8" t="inlineStr"/>
-      <c r="I13" s="9" t="inlineStr"/>
+      <c r="I13" s="9" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
       <c r="J13" s="5" t="inlineStr">
         <is>
-          <t>작업자 / 진행자</t>
-        </is>
-      </c>
-      <c r="K13" s="5" t="inlineStr"/>
+          <t>작업자/진행자</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="n">
@@ -6695,12 +6994,11 @@
           <t>발생 일시</t>
         </is>
       </c>
-      <c r="K14" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:J2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
